--- a/artfynd/A 49333-2025 artfynd.xlsx
+++ b/artfynd/A 49333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100455232</v>
+        <v>93167653</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,26 +709,26 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsnäsvägen, Gstr</t>
+          <t>Ramsnäsv, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570614.6587948323</v>
+        <v>570621</v>
       </c>
       <c r="R2" t="n">
-        <v>6726302.653816859</v>
+        <v>6726260</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-03</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-03</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,338 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Roland Granström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Roland Granström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>116650908</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lövåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570663</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6726118</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100455232</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsnäsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570615</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6726303</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ingrid Kallberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ingrid Kallberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87907520</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ovansjö, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570771</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6726305</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49333-2025 artfynd.xlsx
+++ b/artfynd/A 49333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93167653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116650908</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100455232</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907520</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>